--- a/Team-Data/2007-08/3-10-2007-08.xlsx
+++ b/Team-Data/2007-08/3-10-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,61 +728,61 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" t="n">
         <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>0.413</v>
+        <v>0.419</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="J2" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M2" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.344</v>
+        <v>0.337</v>
       </c>
       <c r="O2" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="P2" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R2" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S2" t="n">
         <v>29.8</v>
       </c>
       <c r="T2" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U2" t="n">
         <v>21.3</v>
       </c>
       <c r="V2" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W2" t="n">
         <v>7.5</v>
@@ -727,19 +794,19 @@
         <v>5.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA2" t="n">
         <v>21.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -754,13 +821,13 @@
         <v>5</v>
       </c>
       <c r="AI2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
         <v>28</v>
@@ -769,13 +836,13 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
         <v>5</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
         <v>7</v>
@@ -784,7 +851,7 @@
         <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
@@ -793,10 +860,10 @@
         <v>16</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX2" t="n">
         <v>3</v>
@@ -805,13 +872,13 @@
         <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.806</v>
+        <v>0.803</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
@@ -861,7 +928,7 @@
         <v>36.2</v>
       </c>
       <c r="J3" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="K3" t="n">
         <v>0.476</v>
@@ -870,7 +937,7 @@
         <v>7.5</v>
       </c>
       <c r="M3" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N3" t="n">
         <v>0.388</v>
@@ -879,7 +946,7 @@
         <v>20.8</v>
       </c>
       <c r="P3" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="Q3" t="n">
         <v>0.768</v>
@@ -888,10 +955,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="U3" t="n">
         <v>22.3</v>
@@ -900,28 +967,28 @@
         <v>15.3</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB3" t="n">
         <v>100.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -969,13 +1036,13 @@
         <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
@@ -990,7 +1057,7 @@
         <v>25</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1118,7 +1185,7 @@
         <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
         <v>19</v>
@@ -1160,7 +1227,7 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
@@ -1175,7 +1242,7 @@
         <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -1285,19 +1352,19 @@
         <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI5" t="n">
         <v>22</v>
@@ -1321,7 +1388,7 @@
         <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
         <v>19</v>
@@ -1357,7 +1424,7 @@
         <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -1389,31 +1456,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" t="n">
         <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>0.578</v>
+        <v>0.571</v>
       </c>
       <c r="H6" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J6" t="n">
-        <v>81.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M6" t="n">
         <v>19.3</v>
@@ -1422,31 +1489,31 @@
         <v>0.366</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="R6" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S6" t="n">
         <v>31.1</v>
       </c>
       <c r="T6" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U6" t="n">
         <v>19.8</v>
       </c>
       <c r="V6" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X6" t="n">
         <v>5</v>
@@ -1455,22 +1522,22 @@
         <v>4.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>97.3</v>
+        <v>97.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
@@ -1479,22 +1546,22 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
         <v>10</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
       </c>
       <c r="AM6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN6" t="n">
         <v>13</v>
@@ -1503,13 +1570,13 @@
         <v>20</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
       </c>
       <c r="AR6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS6" t="n">
         <v>11</v>
@@ -1524,7 +1591,7 @@
         <v>9</v>
       </c>
       <c r="AW6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX6" t="n">
         <v>10</v>
@@ -1533,13 +1600,13 @@
         <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
         <v>23</v>
       </c>
       <c r="BB6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC6" t="n">
         <v>15</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
         <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.641</v>
+        <v>0.635</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1592,37 +1659,37 @@
         <v>79.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L7" t="n">
         <v>5.9</v>
       </c>
       <c r="M7" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O7" t="n">
         <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>11</v>
       </c>
       <c r="S7" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U7" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V7" t="n">
         <v>12.9</v>
@@ -1643,16 +1710,16 @@
         <v>21.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1661,16 +1728,16 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>19</v>
@@ -1700,10 +1767,10 @@
         <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW7" t="n">
         <v>29</v>
@@ -1724,7 +1791,7 @@
         <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.587</v>
+        <v>0.597</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1777,19 +1844,19 @@
         <v>0.459</v>
       </c>
       <c r="L8" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N8" t="n">
         <v>0.344</v>
       </c>
       <c r="O8" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="P8" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0.753</v>
@@ -1804,7 +1871,7 @@
         <v>44.4</v>
       </c>
       <c r="U8" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
         <v>15.2</v>
@@ -1813,7 +1880,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="n">
         <v>5</v>
@@ -1825,13 +1892,13 @@
         <v>24</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.5</v>
+        <v>107.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1876,7 +1943,7 @@
         <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
         <v>3</v>
@@ -1885,10 +1952,10 @@
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2043,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
         <v>12</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2204,7 +2271,7 @@
         <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
@@ -2231,13 +2298,13 @@
         <v>14</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
         <v>17</v>
@@ -2252,7 +2319,7 @@
         <v>7</v>
       </c>
       <c r="AW10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2317,7 +2384,7 @@
         <v>37.1</v>
       </c>
       <c r="J11" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K11" t="n">
         <v>0.455</v>
@@ -2329,22 +2396,22 @@
         <v>20.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O11" t="n">
         <v>16</v>
       </c>
       <c r="P11" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.724</v>
+        <v>0.728</v>
       </c>
       <c r="R11" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S11" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T11" t="n">
         <v>44.5</v>
@@ -2353,31 +2420,31 @@
         <v>22.3</v>
       </c>
       <c r="V11" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W11" t="n">
         <v>7.4</v>
       </c>
       <c r="X11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA11" t="n">
         <v>19.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>97.3</v>
+        <v>97.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2392,13 +2459,13 @@
         <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ11" t="n">
         <v>13</v>
       </c>
       <c r="AK11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL11" t="n">
         <v>11</v>
@@ -2407,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
@@ -2416,19 +2483,19 @@
         <v>27</v>
       </c>
       <c r="AQ11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AR11" t="n">
         <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
         <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
         <v>11</v>
@@ -2440,7 +2507,7 @@
         <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
         <v>4</v>
@@ -2449,7 +2516,7 @@
         <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
         <v>5</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2628,7 +2695,7 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
         <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>0.339</v>
+        <v>0.328</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,19 +2748,19 @@
         <v>34.3</v>
       </c>
       <c r="J13" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L13" t="n">
         <v>4.3</v>
       </c>
       <c r="M13" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.335</v>
+        <v>0.331</v>
       </c>
       <c r="O13" t="n">
         <v>21.1</v>
@@ -2702,19 +2769,19 @@
         <v>26.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="R13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>30.5</v>
       </c>
       <c r="T13" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U13" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V13" t="n">
         <v>14.5</v>
@@ -2726,22 +2793,22 @@
         <v>4.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z13" t="n">
         <v>21.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB13" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5.7</v>
+        <v>-5.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2762,7 +2829,7 @@
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL13" t="n">
         <v>27</v>
@@ -2783,19 +2850,19 @@
         <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS13" t="n">
         <v>15</v>
       </c>
       <c r="AT13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU13" t="n">
         <v>15</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
@@ -2807,13 +2874,13 @@
         <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2992,7 +3059,7 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
@@ -3117,7 +3184,7 @@
         <v>28</v>
       </c>
       <c r="AH15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
         <v>13</v>
@@ -3150,7 +3217,7 @@
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
         <v>20</v>
@@ -3180,7 +3247,7 @@
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" t="n">
         <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>0.177</v>
+        <v>0.18</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,67 +3294,67 @@
         <v>35.5</v>
       </c>
       <c r="J16" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="K16" t="n">
         <v>0.455</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.349</v>
+        <v>0.344</v>
       </c>
       <c r="O16" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P16" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.723</v>
+        <v>0.724</v>
       </c>
       <c r="R16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>28.8</v>
+        <v>29</v>
       </c>
       <c r="T16" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="U16" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V16" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
         <v>7.2</v>
       </c>
       <c r="X16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.8</v>
+        <v>93.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.7</v>
+        <v>-7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3308,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
@@ -3317,7 +3384,7 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>23</v>
@@ -3326,7 +3393,7 @@
         <v>19</v>
       </c>
       <c r="AQ16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3338,7 +3405,7 @@
         <v>30</v>
       </c>
       <c r="AU16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV16" t="n">
         <v>19</v>
@@ -3350,7 +3417,7 @@
         <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
@@ -3359,10 +3426,10 @@
         <v>17</v>
       </c>
       <c r="BB16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3484,7 +3551,7 @@
         <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
         <v>14</v>
@@ -3523,13 +3590,13 @@
         <v>19</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>20</v>
@@ -3538,13 +3605,13 @@
         <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3681,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3690,10 +3757,10 @@
         <v>29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" t="n">
         <v>26</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.406</v>
+        <v>0.413</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="J19" t="n">
         <v>78.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
         <v>5.8</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O19" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P19" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R19" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S19" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T19" t="n">
         <v>42.4</v>
       </c>
       <c r="U19" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W19" t="n">
         <v>6.5</v>
@@ -3818,22 +3885,22 @@
         <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA19" t="n">
         <v>22.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.7</v>
+        <v>94</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.4</v>
+        <v>-5.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -3845,7 +3912,7 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3854,31 +3921,31 @@
         <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>20</v>
       </c>
       <c r="AM19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR19" t="n">
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
         <v>9</v>
@@ -3887,16 +3954,16 @@
         <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
@@ -3905,7 +3972,7 @@
         <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -4015,19 +4082,19 @@
         <v>5</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
       </c>
       <c r="AG20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
@@ -4036,7 +4103,7 @@
         <v>7</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>5</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" t="n">
         <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
-        <v>0.281</v>
+        <v>0.286</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4137,10 +4204,10 @@
         <v>35.3</v>
       </c>
       <c r="J21" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L21" t="n">
         <v>5.8</v>
@@ -4149,16 +4216,16 @@
         <v>17.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O21" t="n">
         <v>19</v>
       </c>
       <c r="P21" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.728</v>
+        <v>0.726</v>
       </c>
       <c r="R21" t="n">
         <v>12.1</v>
@@ -4167,13 +4234,13 @@
         <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U21" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="V21" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W21" t="n">
         <v>6.1</v>
@@ -4191,13 +4258,13 @@
         <v>21</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.3</v>
+        <v>95.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.7</v>
+        <v>-6.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4212,22 +4279,22 @@
         <v>6</v>
       </c>
       <c r="AI21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ21" t="n">
         <v>18</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>16</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>13</v>
@@ -4236,10 +4303,10 @@
         <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
         <v>23</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
         <v>16</v>
@@ -4272,7 +4339,7 @@
         <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -4301,46 +4368,46 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0.631</v>
+        <v>0.625</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J22" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L22" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>24.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.38</v>
+        <v>0.378</v>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P22" t="n">
         <v>29</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.725</v>
+        <v>0.727</v>
       </c>
       <c r="R22" t="n">
         <v>9.5</v>
@@ -4352,10 +4419,10 @@
         <v>42.2</v>
       </c>
       <c r="U22" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W22" t="n">
         <v>6.2</v>
@@ -4367,34 +4434,34 @@
         <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA22" t="n">
         <v>23.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.7</v>
+        <v>104.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF22" t="n">
         <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
         <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ22" t="n">
         <v>27</v>
@@ -4409,7 +4476,7 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO22" t="n">
         <v>7</v>
@@ -4433,19 +4500,19 @@
         <v>24</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
         <v>26</v>
       </c>
       <c r="AX22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -4483,85 +4550,85 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E23" t="n">
         <v>30</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>0.469</v>
+        <v>0.476</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
-        <v>81</v>
+        <v>80.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.464</v>
       </c>
       <c r="L23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.315</v>
+        <v>0.32</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P23" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q23" t="n">
         <v>0.703</v>
       </c>
       <c r="R23" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="S23" t="n">
         <v>29</v>
       </c>
       <c r="T23" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U23" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z23" t="n">
         <v>19.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>16</v>
@@ -4573,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4582,7 +4649,7 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4603,13 +4670,13 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS23" t="n">
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU23" t="n">
         <v>21</v>
@@ -4630,10 +4697,10 @@
         <v>7</v>
       </c>
       <c r="BA23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB23" t="n">
         <v>19</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>21</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>4.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>8</v>
@@ -4797,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
@@ -4812,7 +4879,7 @@
         <v>6</v>
       </c>
       <c r="BA24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -4847,64 +4914,64 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>0.516</v>
+        <v>0.524</v>
       </c>
       <c r="H25" t="n">
         <v>48.7</v>
       </c>
       <c r="I25" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J25" t="n">
         <v>79.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L25" t="n">
         <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O25" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P25" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R25" t="n">
         <v>10.6</v>
       </c>
       <c r="S25" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T25" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
       </c>
       <c r="V25" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X25" t="n">
         <v>4.5</v>
@@ -4913,19 +4980,19 @@
         <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4940,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ25" t="n">
         <v>23</v>
@@ -4949,16 +5016,16 @@
         <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP25" t="n">
         <v>24</v>
@@ -4985,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY25" t="n">
         <v>1</v>
@@ -4994,7 +5061,7 @@
         <v>9</v>
       </c>
       <c r="BA25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB25" t="n">
         <v>25</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,7 +5186,7 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
         <v>15</v>
@@ -5152,10 +5219,10 @@
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU26" t="n">
         <v>28</v>
@@ -5167,7 +5234,7 @@
         <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY26" t="n">
         <v>27</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -5211,43 +5278,43 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F27" t="n">
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.698</v>
+        <v>0.694</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J27" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L27" t="n">
         <v>7.7</v>
       </c>
       <c r="M27" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P27" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q27" t="n">
         <v>0.761</v>
@@ -5262,16 +5329,16 @@
         <v>41.6</v>
       </c>
       <c r="U27" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V27" t="n">
         <v>12.9</v>
       </c>
       <c r="W27" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
         <v>4.4</v>
@@ -5280,25 +5347,25 @@
         <v>19</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC27" t="n">
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
         <v>3</v>
       </c>
       <c r="AG27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH27" t="n">
         <v>24</v>
@@ -5319,7 +5386,7 @@
         <v>7</v>
       </c>
       <c r="AN27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO27" t="n">
         <v>26</v>
@@ -5340,10 +5407,10 @@
         <v>17</v>
       </c>
       <c r="AU27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW27" t="n">
         <v>22</v>
@@ -5358,13 +5425,13 @@
         <v>2</v>
       </c>
       <c r="BA27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB27" t="n">
         <v>23</v>
       </c>
       <c r="BC27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5546,7 +5613,7 @@
         <v>18</v>
       </c>
       <c r="BC28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5665,7 +5732,7 @@
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5716,7 +5783,7 @@
         <v>27</v>
       </c>
       <c r="AY29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ29" t="n">
         <v>8</v>
@@ -5728,7 +5795,7 @@
         <v>10</v>
       </c>
       <c r="BC29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>6.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF30" t="n">
         <v>7</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6032,19 +6099,19 @@
         <v>2</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>13</v>
       </c>
       <c r="AM31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN31" t="n">
         <v>23</v>
@@ -6065,7 +6132,7 @@
         <v>22</v>
       </c>
       <c r="AT31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU31" t="n">
         <v>29</v>
@@ -6080,13 +6147,13 @@
         <v>8</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-10-2007-08</t>
+          <t>2008-03-10</t>
         </is>
       </c>
     </row>
